--- a/Evaluations/Experimental Results/output_figures/category_overview.xlsx
+++ b/Evaluations/Experimental Results/output_figures/category_overview.xlsx
@@ -420,7 +420,7 @@
         <v>12.92613636363636</v>
       </c>
       <c r="E2">
-        <v>34.63125</v>
+        <v>34.659375</v>
       </c>
     </row>
     <row r="3" spans="1:5">
